--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260602_221934.xlsx
@@ -5590,7 +5590,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8274,7 +8274,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
